--- a/cypress/fixtures/PerfilEcoInfFinanciera.xlsx
+++ b/cypress/fixtures/PerfilEcoInfFinanciera.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>Moneda</t>
   </si>
@@ -28,7 +28,10 @@
     <t>Lempira</t>
   </si>
   <si>
-    <t>prueba qa</t>
+    <t>100000000</t>
+  </si>
+  <si>
+    <t>pruebas automatizadas</t>
   </si>
 </sst>
 </file>
@@ -94,12 +97,12 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -317,7 +320,7 @@
   <cols>
     <col customWidth="1" min="2" max="2" width="18.88"/>
     <col customWidth="1" min="3" max="3" width="14.75"/>
-    <col customWidth="1" min="4" max="4" width="13.0"/>
+    <col customWidth="1" min="4" max="4" width="30.88"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -338,14 +341,14 @@
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3">
-        <v>1.0E8</v>
+      <c r="B2" s="3" t="s">
+        <v>5</v>
       </c>
-      <c r="C2" s="3">
-        <v>1.0E8</v>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
